--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -4482,10 +4482,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950718</v>
+        <v>119950729</v>
       </c>
       <c r="B35" t="n">
-        <v>94681</v>
+        <v>5485</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4494,31 +4494,36 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>101410</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4526,7 +4531,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588792</v>
+        <v>588786</v>
       </c>
       <c r="R35" t="n">
         <v>6378207</v>
@@ -4599,10 +4604,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119951016</v>
+        <v>119950718</v>
       </c>
       <c r="B36" t="n">
-        <v>91832</v>
+        <v>94681</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4611,34 +4616,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4646,10 +4648,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589034</v>
+        <v>588792</v>
       </c>
       <c r="R36" t="n">
-        <v>6377962</v>
+        <v>6378207</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4719,10 +4721,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119950729</v>
+        <v>119951016</v>
       </c>
       <c r="B37" t="n">
-        <v>5485</v>
+        <v>91832</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4735,21 +4737,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101410</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4759,8 +4761,6 @@
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588786</v>
+        <v>589034</v>
       </c>
       <c r="R37" t="n">
-        <v>6378207</v>
+        <v>6377962</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119789982</v>
+        <v>119789934</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589045</v>
+        <v>588849</v>
       </c>
       <c r="R2" t="n">
-        <v>6377954</v>
+        <v>6378218</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119789969</v>
+        <v>119790007</v>
       </c>
       <c r="B3" t="n">
-        <v>94681</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,27 +804,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589092</v>
+        <v>589019</v>
       </c>
       <c r="R3" t="n">
-        <v>6377970</v>
+        <v>6377960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +883,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119790043</v>
+        <v>119790021</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,39 +914,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,7 +959,7 @@
         <v>6378039</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,6 +997,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119790021</v>
+        <v>119790089</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,30 +1028,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1060,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588905</v>
+        <v>588906</v>
       </c>
       <c r="R5" t="n">
-        <v>6378039</v>
+        <v>6378054</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119789953</v>
+        <v>119789941</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1142,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1174,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588908</v>
+        <v>588925</v>
       </c>
       <c r="R6" t="n">
-        <v>6378028</v>
+        <v>6378093</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119790089</v>
+        <v>119790043</v>
       </c>
       <c r="B7" t="n">
-        <v>90582</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,21 +1259,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,12 +1281,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,13 +1295,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588906</v>
+        <v>588905</v>
       </c>
       <c r="R7" t="n">
-        <v>6378054</v>
+        <v>6378039</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1339,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1350,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119789941</v>
+        <v>119789982</v>
       </c>
       <c r="B8" t="n">
-        <v>90582</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1401,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588925</v>
+        <v>589045</v>
       </c>
       <c r="R8" t="n">
-        <v>6378093</v>
+        <v>6377954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,6 +1452,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1463,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119789934</v>
+        <v>119789969</v>
       </c>
       <c r="B9" t="n">
-        <v>91883</v>
+        <v>94681</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,38 +1483,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1514,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588849</v>
+        <v>589092</v>
       </c>
       <c r="R9" t="n">
-        <v>6378218</v>
+        <v>6377970</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,7 +1577,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119790007</v>
+        <v>119789953</v>
       </c>
       <c r="B10" t="n">
         <v>91840</v>
@@ -1627,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589019</v>
+        <v>588908</v>
       </c>
       <c r="R10" t="n">
-        <v>6377960</v>
+        <v>6378028</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1672,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119895508</v>
+        <v>119894264</v>
       </c>
       <c r="B11" t="n">
-        <v>91832</v>
+        <v>57326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,48 +1706,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588905</v>
+        <v>589103</v>
       </c>
       <c r="R11" t="n">
-        <v>6378030</v>
+        <v>6377996</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1784,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1814,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119894264</v>
+        <v>119895883</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>94681</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,25 +1814,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,13 +1842,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589103</v>
+        <v>589100</v>
       </c>
       <c r="R12" t="n">
-        <v>6377996</v>
+        <v>6378008</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119895525</v>
+        <v>119894432</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,50 +1926,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588912</v>
+        <v>589148</v>
       </c>
       <c r="R13" t="n">
-        <v>6378042</v>
+        <v>6378016</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2010,7 +1994,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2004,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2159,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119895883</v>
+        <v>119895508</v>
       </c>
       <c r="B15" t="n">
-        <v>94681</v>
+        <v>91832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,38 +2155,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589100</v>
+        <v>588905</v>
       </c>
       <c r="R15" t="n">
-        <v>6378008</v>
+        <v>6378030</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2234,7 +2229,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2239,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,6 +2248,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2383,10 +2379,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119894432</v>
+        <v>119895576</v>
       </c>
       <c r="B17" t="n">
-        <v>57463</v>
+        <v>94681</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,46 +2391,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589148</v>
+        <v>588943</v>
       </c>
       <c r="R17" t="n">
-        <v>6378016</v>
+        <v>6378050</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,7 +2454,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2464,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,7 +2491,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119895576</v>
+        <v>119894515</v>
       </c>
       <c r="B18" t="n">
         <v>94681</v>
@@ -2536,14 +2527,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588943</v>
+        <v>589143</v>
       </c>
       <c r="R18" t="n">
-        <v>6378050</v>
+        <v>6378011</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2575,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119894515</v>
+        <v>119895525</v>
       </c>
       <c r="B19" t="n">
-        <v>94681</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2628,34 +2619,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589143</v>
+        <v>588912</v>
       </c>
       <c r="R19" t="n">
-        <v>6378011</v>
+        <v>6378042</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2845,7 +2845,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119950915</v>
+        <v>119950823</v>
       </c>
       <c r="B21" t="n">
         <v>79144</v>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588998</v>
+        <v>588879</v>
       </c>
       <c r="R21" t="n">
-        <v>6377948</v>
+        <v>6378129</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119951055</v>
+        <v>119950809</v>
       </c>
       <c r="B22" t="n">
         <v>79144</v>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588879</v>
+        <v>588881</v>
       </c>
       <c r="R22" t="n">
-        <v>6377973</v>
+        <v>6378203</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3077,7 +3077,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950738</v>
+        <v>119950796</v>
       </c>
       <c r="B23" t="n">
         <v>79144</v>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588797</v>
+        <v>588888</v>
       </c>
       <c r="R23" t="n">
-        <v>6378202</v>
+        <v>6378207</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3193,7 +3193,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119950786</v>
+        <v>119950738</v>
       </c>
       <c r="B24" t="n">
         <v>79144</v>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588866</v>
+        <v>588797</v>
       </c>
       <c r="R24" t="n">
-        <v>6378218</v>
+        <v>6378202</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119950865</v>
+        <v>119951055</v>
       </c>
       <c r="B25" t="n">
         <v>79144</v>
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588863</v>
+        <v>588879</v>
       </c>
       <c r="R25" t="n">
-        <v>6378059</v>
+        <v>6377973</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119950884</v>
+        <v>119950729</v>
       </c>
       <c r="B26" t="n">
-        <v>90582</v>
+        <v>5485</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3465,6 +3465,8 @@
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3472,10 +3474,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588870</v>
+        <v>588786</v>
       </c>
       <c r="R26" t="n">
-        <v>6377977</v>
+        <v>6378207</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3665,10 +3667,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119951014</v>
+        <v>119951024</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>79144</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3681,28 +3683,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3712,10 +3710,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589030</v>
+        <v>588886</v>
       </c>
       <c r="R28" t="n">
-        <v>6377964</v>
+        <v>6377979</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3785,7 +3783,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950823</v>
+        <v>119950786</v>
       </c>
       <c r="B29" t="n">
         <v>79144</v>
@@ -3828,10 +3826,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588879</v>
+        <v>588866</v>
       </c>
       <c r="R29" t="n">
-        <v>6378129</v>
+        <v>6378218</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4018,7 +4016,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950809</v>
+        <v>119950915</v>
       </c>
       <c r="B31" t="n">
         <v>79144</v>
@@ -4061,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588881</v>
+        <v>588998</v>
       </c>
       <c r="R31" t="n">
-        <v>6378203</v>
+        <v>6377948</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4134,7 +4132,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119951024</v>
+        <v>119950713</v>
       </c>
       <c r="B32" t="n">
         <v>79144</v>
@@ -4177,10 +4175,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588886</v>
+        <v>588800</v>
       </c>
       <c r="R32" t="n">
-        <v>6377979</v>
+        <v>6378217</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4250,10 +4248,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950873</v>
+        <v>119950884</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>90582</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4266,24 +4264,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4293,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588864</v>
+        <v>588870</v>
       </c>
       <c r="R33" t="n">
-        <v>6378060</v>
+        <v>6377977</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4366,10 +4368,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950796</v>
+        <v>119951016</v>
       </c>
       <c r="B34" t="n">
-        <v>79144</v>
+        <v>91832</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4382,24 +4384,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4409,10 +4415,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588888</v>
+        <v>589034</v>
       </c>
       <c r="R34" t="n">
-        <v>6378207</v>
+        <v>6377962</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4482,10 +4488,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950729</v>
+        <v>119951014</v>
       </c>
       <c r="B35" t="n">
-        <v>5485</v>
+        <v>91832</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4498,21 +4504,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101410</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4522,8 +4528,6 @@
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4531,10 +4535,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588786</v>
+        <v>589030</v>
       </c>
       <c r="R35" t="n">
-        <v>6378207</v>
+        <v>6377964</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4721,10 +4725,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119951016</v>
+        <v>119950873</v>
       </c>
       <c r="B37" t="n">
-        <v>91832</v>
+        <v>79144</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4737,28 +4741,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589034</v>
+        <v>588864</v>
       </c>
       <c r="R37" t="n">
-        <v>6377962</v>
+        <v>6378060</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119950713</v>
+        <v>119950865</v>
       </c>
       <c r="B38" t="n">
         <v>79144</v>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588800</v>
+        <v>588863</v>
       </c>
       <c r="R38" t="n">
-        <v>6378217</v>
+        <v>6378059</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119789934</v>
+        <v>119789969</v>
       </c>
       <c r="B2" t="n">
-        <v>91883</v>
+        <v>94681</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588849</v>
+        <v>589092</v>
       </c>
       <c r="R2" t="n">
-        <v>6378218</v>
+        <v>6377970</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -902,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119790021</v>
+        <v>119790043</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,38 +907,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,7 +953,7 @@
         <v>6378039</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +991,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119790089</v>
+        <v>119789941</v>
       </c>
       <c r="B5" t="n">
         <v>90582</v>
@@ -1067,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588906</v>
+        <v>588925</v>
       </c>
       <c r="R5" t="n">
-        <v>6378054</v>
+        <v>6378093</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1130,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119789941</v>
+        <v>119789934</v>
       </c>
       <c r="B6" t="n">
-        <v>90582</v>
+        <v>91883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1170,7 +1162,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1181,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588925</v>
+        <v>588849</v>
       </c>
       <c r="R6" t="n">
-        <v>6378093</v>
+        <v>6378218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119790043</v>
+        <v>119789982</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1281,13 +1273,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1295,13 +1286,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588905</v>
+        <v>589045</v>
       </c>
       <c r="R7" t="n">
-        <v>6378039</v>
+        <v>6377954</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,6 +1330,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1357,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119789982</v>
+        <v>119790089</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1361,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1408,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589045</v>
+        <v>588906</v>
       </c>
       <c r="R8" t="n">
-        <v>6377954</v>
+        <v>6378054</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119789969</v>
+        <v>119790021</v>
       </c>
       <c r="B9" t="n">
-        <v>94681</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,27 +1479,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1515,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589092</v>
+        <v>588905</v>
       </c>
       <c r="R9" t="n">
-        <v>6377970</v>
+        <v>6378039</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,6 +1558,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119894264</v>
+        <v>119895508</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>91832</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,37 +1706,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589103</v>
+        <v>588905</v>
       </c>
       <c r="R11" t="n">
-        <v>6377996</v>
+        <v>6378030</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,6 +1795,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1802,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119895883</v>
+        <v>119894432</v>
       </c>
       <c r="B12" t="n">
-        <v>94681</v>
+        <v>57463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,41 +1826,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589100</v>
+        <v>589148</v>
       </c>
       <c r="R12" t="n">
-        <v>6378008</v>
+        <v>6378016</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119894432</v>
+        <v>119894515</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>94681</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,46 +1943,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589148</v>
+        <v>589143</v>
       </c>
       <c r="R13" t="n">
-        <v>6378016</v>
+        <v>6378011</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2004,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2143,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119895508</v>
+        <v>119894264</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>57326</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,48 +2171,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588905</v>
+        <v>589103</v>
       </c>
       <c r="R15" t="n">
-        <v>6378030</v>
+        <v>6377996</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2229,7 +2230,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2239,7 +2240,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,7 +2249,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119895405</v>
+        <v>119895576</v>
       </c>
       <c r="B16" t="n">
-        <v>90582</v>
+        <v>94681</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,25 +2279,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,13 +2307,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588908</v>
+        <v>588943</v>
       </c>
       <c r="R16" t="n">
-        <v>6378060</v>
+        <v>6378050</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,7 +2379,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119895576</v>
+        <v>119895685</v>
       </c>
       <c r="B17" t="n">
         <v>94681</v>
@@ -2412,17 +2412,26 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588943</v>
+        <v>589007</v>
       </c>
       <c r="R17" t="n">
-        <v>6378050</v>
+        <v>6378030</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2454,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,7 +2500,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119894515</v>
+        <v>119895883</v>
       </c>
       <c r="B18" t="n">
         <v>94681</v>
@@ -2531,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589143</v>
+        <v>589100</v>
       </c>
       <c r="R18" t="n">
-        <v>6378011</v>
+        <v>6378008</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2566,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119895525</v>
+        <v>119895405</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,50 +2624,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588912</v>
+        <v>588908</v>
       </c>
       <c r="R19" t="n">
-        <v>6378042</v>
+        <v>6378060</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119895685</v>
+        <v>119895525</v>
       </c>
       <c r="B20" t="n">
-        <v>94681</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589007</v>
+        <v>588912</v>
       </c>
       <c r="R20" t="n">
-        <v>6378030</v>
+        <v>6378042</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119950823</v>
+        <v>119951016</v>
       </c>
       <c r="B21" t="n">
-        <v>79144</v>
+        <v>91832</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,24 +2861,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2888,10 +2892,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588879</v>
+        <v>589034</v>
       </c>
       <c r="R21" t="n">
-        <v>6378129</v>
+        <v>6377962</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2961,7 +2965,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119950809</v>
+        <v>119950915</v>
       </c>
       <c r="B22" t="n">
         <v>79144</v>
@@ -3004,10 +3008,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588881</v>
+        <v>588998</v>
       </c>
       <c r="R22" t="n">
-        <v>6378203</v>
+        <v>6377948</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3077,10 +3081,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950796</v>
+        <v>119950815</v>
       </c>
       <c r="B23" t="n">
-        <v>79144</v>
+        <v>94681</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3089,30 +3093,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3120,10 +3125,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588888</v>
+        <v>588881</v>
       </c>
       <c r="R23" t="n">
-        <v>6378207</v>
+        <v>6378203</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3309,7 +3314,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119951055</v>
+        <v>119950865</v>
       </c>
       <c r="B25" t="n">
         <v>79144</v>
@@ -3352,10 +3357,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588879</v>
+        <v>588863</v>
       </c>
       <c r="R25" t="n">
-        <v>6377973</v>
+        <v>6378059</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3425,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119950729</v>
+        <v>119951024</v>
       </c>
       <c r="B26" t="n">
-        <v>5485</v>
+        <v>79144</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3441,32 +3446,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3474,10 +3473,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588786</v>
+        <v>588886</v>
       </c>
       <c r="R26" t="n">
-        <v>6378207</v>
+        <v>6377979</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3547,10 +3546,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119951000</v>
+        <v>119950713</v>
       </c>
       <c r="B27" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,28 +3562,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3594,10 +3589,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588820</v>
+        <v>588800</v>
       </c>
       <c r="R27" t="n">
-        <v>6378230</v>
+        <v>6378217</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3667,7 +3662,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119951024</v>
+        <v>119950823</v>
       </c>
       <c r="B28" t="n">
         <v>79144</v>
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588886</v>
+        <v>588879</v>
       </c>
       <c r="R28" t="n">
-        <v>6377979</v>
+        <v>6378129</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3783,10 +3778,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950786</v>
+        <v>119950729</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
+        <v>5485</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3799,26 +3794,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3826,10 +3827,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588866</v>
+        <v>588786</v>
       </c>
       <c r="R29" t="n">
-        <v>6378218</v>
+        <v>6378207</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3899,10 +3900,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950815</v>
+        <v>119950786</v>
       </c>
       <c r="B30" t="n">
-        <v>94681</v>
+        <v>79144</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,31 +3912,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588881</v>
+        <v>588866</v>
       </c>
       <c r="R30" t="n">
-        <v>6378203</v>
+        <v>6378218</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950915</v>
+        <v>119950718</v>
       </c>
       <c r="B31" t="n">
-        <v>79144</v>
+        <v>94681</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4028,30 +4028,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4059,10 +4060,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588998</v>
+        <v>588792</v>
       </c>
       <c r="R31" t="n">
-        <v>6377948</v>
+        <v>6378207</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4132,7 +4133,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950713</v>
+        <v>119950873</v>
       </c>
       <c r="B32" t="n">
         <v>79144</v>
@@ -4175,10 +4176,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588800</v>
+        <v>588864</v>
       </c>
       <c r="R32" t="n">
-        <v>6378217</v>
+        <v>6378060</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4248,10 +4249,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950884</v>
+        <v>119951000</v>
       </c>
       <c r="B33" t="n">
-        <v>90582</v>
+        <v>91884</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4264,26 +4265,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4295,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588870</v>
+        <v>588820</v>
       </c>
       <c r="R33" t="n">
-        <v>6377977</v>
+        <v>6378230</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4368,10 +4369,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119951016</v>
+        <v>119950796</v>
       </c>
       <c r="B34" t="n">
-        <v>91832</v>
+        <v>79144</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4384,28 +4385,24 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4415,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589034</v>
+        <v>588888</v>
       </c>
       <c r="R34" t="n">
-        <v>6377962</v>
+        <v>6378207</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4488,10 +4485,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119951014</v>
+        <v>119950809</v>
       </c>
       <c r="B35" t="n">
-        <v>91832</v>
+        <v>79144</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4504,28 +4501,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4535,10 +4528,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589030</v>
+        <v>588881</v>
       </c>
       <c r="R35" t="n">
-        <v>6377964</v>
+        <v>6378203</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4608,10 +4601,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119950718</v>
+        <v>119951014</v>
       </c>
       <c r="B36" t="n">
-        <v>94681</v>
+        <v>91832</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4620,31 +4613,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4652,10 +4648,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588792</v>
+        <v>589030</v>
       </c>
       <c r="R36" t="n">
-        <v>6378207</v>
+        <v>6377964</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4725,7 +4721,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119950873</v>
+        <v>119951055</v>
       </c>
       <c r="B37" t="n">
         <v>79144</v>
@@ -4768,10 +4764,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588864</v>
+        <v>588879</v>
       </c>
       <c r="R37" t="n">
-        <v>6378060</v>
+        <v>6377973</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4841,10 +4837,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119950865</v>
+        <v>119950884</v>
       </c>
       <c r="B38" t="n">
-        <v>79144</v>
+        <v>90582</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4857,24 +4853,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588863</v>
+        <v>588870</v>
       </c>
       <c r="R38" t="n">
-        <v>6378059</v>
+        <v>6377977</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -3081,10 +3081,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950815</v>
+        <v>119950738</v>
       </c>
       <c r="B23" t="n">
-        <v>94681</v>
+        <v>79144</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3093,31 +3093,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3125,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588881</v>
+        <v>588797</v>
       </c>
       <c r="R23" t="n">
-        <v>6378203</v>
+        <v>6378202</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3198,10 +3197,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119950738</v>
+        <v>119950815</v>
       </c>
       <c r="B24" t="n">
-        <v>79144</v>
+        <v>94681</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3210,30 +3209,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588797</v>
+        <v>588881</v>
       </c>
       <c r="R24" t="n">
-        <v>6378202</v>
+        <v>6378203</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950718</v>
+        <v>119950873</v>
       </c>
       <c r="B31" t="n">
-        <v>94681</v>
+        <v>79144</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4028,31 +4028,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4060,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588792</v>
+        <v>588864</v>
       </c>
       <c r="R31" t="n">
-        <v>6378207</v>
+        <v>6378060</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4133,10 +4132,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950873</v>
+        <v>119951000</v>
       </c>
       <c r="B32" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4149,24 +4148,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -4176,10 +4179,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588864</v>
+        <v>588820</v>
       </c>
       <c r="R32" t="n">
-        <v>6378060</v>
+        <v>6378230</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4249,10 +4252,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119951000</v>
+        <v>119950718</v>
       </c>
       <c r="B33" t="n">
-        <v>91884</v>
+        <v>94681</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4261,34 +4264,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588820</v>
+        <v>588792</v>
       </c>
       <c r="R33" t="n">
-        <v>6378230</v>
+        <v>6378207</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4369,7 +4369,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950796</v>
+        <v>119950809</v>
       </c>
       <c r="B34" t="n">
         <v>79144</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588888</v>
+        <v>588881</v>
       </c>
       <c r="R34" t="n">
-        <v>6378207</v>
+        <v>6378203</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4485,7 +4485,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950809</v>
+        <v>119950796</v>
       </c>
       <c r="B35" t="n">
         <v>79144</v>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588881</v>
+        <v>588888</v>
       </c>
       <c r="R35" t="n">
-        <v>6378203</v>
+        <v>6378207</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119789969</v>
+        <v>119789934</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
+        <v>91883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589092</v>
+        <v>588849</v>
       </c>
       <c r="R2" t="n">
-        <v>6377970</v>
+        <v>6378218</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +788,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119790007</v>
+        <v>119789953</v>
       </c>
       <c r="B3" t="n">
         <v>91840</v>
@@ -832,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589019</v>
+        <v>588908</v>
       </c>
       <c r="R3" t="n">
-        <v>6377960</v>
+        <v>6378028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +883,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119790043</v>
+        <v>119790007</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,25 +913,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -933,13 +939,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588905</v>
+        <v>589019</v>
       </c>
       <c r="R4" t="n">
-        <v>6378039</v>
+        <v>6377960</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119789941</v>
+        <v>119789982</v>
       </c>
       <c r="B5" t="n">
-        <v>90582</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588925</v>
+        <v>589045</v>
       </c>
       <c r="R5" t="n">
-        <v>6378093</v>
+        <v>6377954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,6 +1110,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119789934</v>
+        <v>119789941</v>
       </c>
       <c r="B6" t="n">
-        <v>91883</v>
+        <v>90582</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1162,7 +1169,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1173,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588849</v>
+        <v>588925</v>
       </c>
       <c r="R6" t="n">
-        <v>6378218</v>
+        <v>6378093</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119789982</v>
+        <v>119789969</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>94681</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1258,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589045</v>
+        <v>589092</v>
       </c>
       <c r="R7" t="n">
-        <v>6377954</v>
+        <v>6377970</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1349,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119790089</v>
+        <v>119790043</v>
       </c>
       <c r="B8" t="n">
-        <v>90582</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,21 +1364,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1387,12 +1386,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588906</v>
+        <v>588905</v>
       </c>
       <c r="R8" t="n">
-        <v>6378054</v>
+        <v>6378039</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1444,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1577,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119789953</v>
+        <v>119790089</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,25 +1588,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1628,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588908</v>
+        <v>588906</v>
       </c>
       <c r="R10" t="n">
-        <v>6378028</v>
+        <v>6378054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,6 +1671,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119895508</v>
+        <v>119895576</v>
       </c>
       <c r="B11" t="n">
-        <v>91832</v>
+        <v>94681</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,49 +1702,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588905</v>
+        <v>588943</v>
       </c>
       <c r="R11" t="n">
-        <v>6378030</v>
+        <v>6378050</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1776,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1784,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1814,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119894432</v>
+        <v>119894264</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,39 +1818,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589148</v>
+        <v>589103</v>
       </c>
       <c r="R12" t="n">
-        <v>6378016</v>
+        <v>6377996</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119894515</v>
+        <v>119895525</v>
       </c>
       <c r="B13" t="n">
-        <v>94681</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,34 +1930,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589143</v>
+        <v>588912</v>
       </c>
       <c r="R13" t="n">
-        <v>6378011</v>
+        <v>6378042</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2006,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119895306</v>
+        <v>119895508</v>
       </c>
       <c r="B14" t="n">
-        <v>90582</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,34 +2051,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588929</v>
+        <v>588905</v>
       </c>
       <c r="R14" t="n">
-        <v>6378092</v>
+        <v>6378030</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2118,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,6 +2140,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119894264</v>
+        <v>119895685</v>
       </c>
       <c r="B15" t="n">
-        <v>57326</v>
+        <v>94681</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,41 +2171,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589103</v>
+        <v>589007</v>
       </c>
       <c r="R15" t="n">
-        <v>6377996</v>
+        <v>6378030</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2230,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,7 +2280,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119895576</v>
+        <v>119895883</v>
       </c>
       <c r="B16" t="n">
         <v>94681</v>
@@ -2303,14 +2316,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588943</v>
+        <v>589100</v>
       </c>
       <c r="R16" t="n">
-        <v>6378050</v>
+        <v>6378008</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2342,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119895685</v>
+        <v>119895405</v>
       </c>
       <c r="B17" t="n">
-        <v>94681</v>
+        <v>90582</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,50 +2404,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589007</v>
+        <v>588908</v>
       </c>
       <c r="R17" t="n">
-        <v>6378030</v>
+        <v>6378060</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119895883</v>
+        <v>119895306</v>
       </c>
       <c r="B18" t="n">
-        <v>94681</v>
+        <v>90582</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,38 +2516,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589100</v>
+        <v>588929</v>
       </c>
       <c r="R18" t="n">
-        <v>6378008</v>
+        <v>6378092</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2575,7 +2579,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2589,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2616,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119895405</v>
+        <v>119894515</v>
       </c>
       <c r="B19" t="n">
-        <v>90582</v>
+        <v>94681</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,41 +2628,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588908</v>
+        <v>589143</v>
       </c>
       <c r="R19" t="n">
-        <v>6378060</v>
+        <v>6378011</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2687,7 +2691,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2701,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2728,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119895525</v>
+        <v>119894432</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,50 +2740,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588912</v>
+        <v>589148</v>
       </c>
       <c r="R20" t="n">
-        <v>6378042</v>
+        <v>6378016</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119951016</v>
+        <v>119950873</v>
       </c>
       <c r="B21" t="n">
-        <v>91832</v>
+        <v>79144</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,28 +2861,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2892,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589034</v>
+        <v>588864</v>
       </c>
       <c r="R21" t="n">
-        <v>6377962</v>
+        <v>6378060</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2965,10 +2961,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119950915</v>
+        <v>119951016</v>
       </c>
       <c r="B22" t="n">
-        <v>79144</v>
+        <v>91832</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2981,24 +2977,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588998</v>
+        <v>589034</v>
       </c>
       <c r="R22" t="n">
-        <v>6377948</v>
+        <v>6377962</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950738</v>
+        <v>119951024</v>
       </c>
       <c r="B23" t="n">
         <v>79144</v>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588797</v>
+        <v>588886</v>
       </c>
       <c r="R23" t="n">
-        <v>6378202</v>
+        <v>6377979</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119950815</v>
+        <v>119950865</v>
       </c>
       <c r="B24" t="n">
-        <v>94681</v>
+        <v>79144</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3209,31 +3209,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3241,10 +3240,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588881</v>
+        <v>588863</v>
       </c>
       <c r="R24" t="n">
-        <v>6378203</v>
+        <v>6378059</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3314,10 +3313,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119950865</v>
+        <v>119951000</v>
       </c>
       <c r="B25" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3330,24 +3329,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3357,10 +3360,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588863</v>
+        <v>588820</v>
       </c>
       <c r="R25" t="n">
-        <v>6378059</v>
+        <v>6378230</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3430,10 +3433,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119951024</v>
+        <v>119951014</v>
       </c>
       <c r="B26" t="n">
-        <v>79144</v>
+        <v>91832</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,24 +3449,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3473,10 +3480,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588886</v>
+        <v>589030</v>
       </c>
       <c r="R26" t="n">
-        <v>6377979</v>
+        <v>6377964</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3662,7 +3669,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119950823</v>
+        <v>119951055</v>
       </c>
       <c r="B28" t="n">
         <v>79144</v>
@@ -3708,7 +3715,7 @@
         <v>588879</v>
       </c>
       <c r="R28" t="n">
-        <v>6378129</v>
+        <v>6377973</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3778,10 +3785,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950729</v>
+        <v>119950796</v>
       </c>
       <c r="B29" t="n">
-        <v>5485</v>
+        <v>79144</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3794,32 +3801,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3827,7 +3828,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588786</v>
+        <v>588888</v>
       </c>
       <c r="R29" t="n">
         <v>6378207</v>
@@ -3900,7 +3901,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950786</v>
+        <v>119950738</v>
       </c>
       <c r="B30" t="n">
         <v>79144</v>
@@ -3943,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588866</v>
+        <v>588797</v>
       </c>
       <c r="R30" t="n">
-        <v>6378218</v>
+        <v>6378202</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4016,7 +4017,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950873</v>
+        <v>119950786</v>
       </c>
       <c r="B31" t="n">
         <v>79144</v>
@@ -4059,10 +4060,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588864</v>
+        <v>588866</v>
       </c>
       <c r="R31" t="n">
-        <v>6378060</v>
+        <v>6378218</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4132,10 +4133,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119951000</v>
+        <v>119950884</v>
       </c>
       <c r="B32" t="n">
-        <v>91884</v>
+        <v>90582</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4148,26 +4149,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -4179,10 +4180,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588820</v>
+        <v>588870</v>
       </c>
       <c r="R32" t="n">
-        <v>6378230</v>
+        <v>6377977</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4252,7 +4253,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950718</v>
+        <v>119950815</v>
       </c>
       <c r="B33" t="n">
         <v>94681</v>
@@ -4296,10 +4297,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588792</v>
+        <v>588881</v>
       </c>
       <c r="R33" t="n">
-        <v>6378207</v>
+        <v>6378203</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4369,7 +4370,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950809</v>
+        <v>119950915</v>
       </c>
       <c r="B34" t="n">
         <v>79144</v>
@@ -4412,10 +4413,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588881</v>
+        <v>588998</v>
       </c>
       <c r="R34" t="n">
-        <v>6378203</v>
+        <v>6377948</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4485,7 +4486,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950796</v>
+        <v>119950823</v>
       </c>
       <c r="B35" t="n">
         <v>79144</v>
@@ -4528,10 +4529,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588888</v>
+        <v>588879</v>
       </c>
       <c r="R35" t="n">
-        <v>6378207</v>
+        <v>6378129</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4601,10 +4602,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119951014</v>
+        <v>119950729</v>
       </c>
       <c r="B36" t="n">
-        <v>91832</v>
+        <v>5485</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4617,21 +4618,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>101410</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4641,6 +4642,8 @@
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4648,10 +4651,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589030</v>
+        <v>588786</v>
       </c>
       <c r="R36" t="n">
-        <v>6377964</v>
+        <v>6378207</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4721,7 +4724,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119951055</v>
+        <v>119950809</v>
       </c>
       <c r="B37" t="n">
         <v>79144</v>
@@ -4764,10 +4767,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588879</v>
+        <v>588881</v>
       </c>
       <c r="R37" t="n">
-        <v>6377973</v>
+        <v>6378203</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4837,10 +4840,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119950884</v>
+        <v>119950718</v>
       </c>
       <c r="B38" t="n">
-        <v>90582</v>
+        <v>94681</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4849,34 +4852,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588870</v>
+        <v>588792</v>
       </c>
       <c r="R38" t="n">
-        <v>6377977</v>
+        <v>6378207</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -2159,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119895685</v>
+        <v>119895405</v>
       </c>
       <c r="B15" t="n">
-        <v>94681</v>
+        <v>90582</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,50 +2171,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589007</v>
+        <v>588908</v>
       </c>
       <c r="R15" t="n">
-        <v>6378030</v>
+        <v>6378060</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,7 +2271,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119895883</v>
+        <v>119895685</v>
       </c>
       <c r="B16" t="n">
         <v>94681</v>
@@ -2313,17 +2304,26 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589100</v>
+        <v>589007</v>
       </c>
       <c r="R16" t="n">
-        <v>6378008</v>
+        <v>6378030</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119895405</v>
+        <v>119895883</v>
       </c>
       <c r="B17" t="n">
-        <v>90582</v>
+        <v>94681</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,41 +2404,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588908</v>
+        <v>589100</v>
       </c>
       <c r="R17" t="n">
-        <v>6378060</v>
+        <v>6378008</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950884</v>
+        <v>119950815</v>
       </c>
       <c r="B32" t="n">
-        <v>90582</v>
+        <v>94681</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4145,34 +4145,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4180,10 +4177,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588870</v>
+        <v>588881</v>
       </c>
       <c r="R32" t="n">
-        <v>6377977</v>
+        <v>6378203</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4253,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950815</v>
+        <v>119950884</v>
       </c>
       <c r="B33" t="n">
-        <v>94681</v>
+        <v>90582</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4265,31 +4262,34 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588881</v>
+        <v>588870</v>
       </c>
       <c r="R33" t="n">
-        <v>6378203</v>
+        <v>6377977</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -2159,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119895405</v>
+        <v>119895685</v>
       </c>
       <c r="B15" t="n">
-        <v>90582</v>
+        <v>94681</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,41 +2171,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588908</v>
+        <v>589007</v>
       </c>
       <c r="R15" t="n">
-        <v>6378060</v>
+        <v>6378030</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2234,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,7 +2280,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119895685</v>
+        <v>119895883</v>
       </c>
       <c r="B16" t="n">
         <v>94681</v>
@@ -2304,26 +2313,17 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589007</v>
+        <v>589100</v>
       </c>
       <c r="R16" t="n">
-        <v>6378030</v>
+        <v>6378008</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119895883</v>
+        <v>119895405</v>
       </c>
       <c r="B17" t="n">
-        <v>94681</v>
+        <v>90582</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,41 +2404,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589100</v>
+        <v>588908</v>
       </c>
       <c r="R17" t="n">
-        <v>6378008</v>
+        <v>6378060</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -2159,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119895685</v>
+        <v>119895405</v>
       </c>
       <c r="B15" t="n">
-        <v>94681</v>
+        <v>90582</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,50 +2171,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589007</v>
+        <v>588908</v>
       </c>
       <c r="R15" t="n">
-        <v>6378030</v>
+        <v>6378060</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,7 +2271,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119895883</v>
+        <v>119895685</v>
       </c>
       <c r="B16" t="n">
         <v>94681</v>
@@ -2313,17 +2304,26 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589100</v>
+        <v>589007</v>
       </c>
       <c r="R16" t="n">
-        <v>6378008</v>
+        <v>6378030</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119895405</v>
+        <v>119895883</v>
       </c>
       <c r="B17" t="n">
-        <v>90582</v>
+        <v>94681</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,41 +2404,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588908</v>
+        <v>589100</v>
       </c>
       <c r="R17" t="n">
-        <v>6378060</v>
+        <v>6378008</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119789934</v>
+        <v>119789941</v>
       </c>
       <c r="B2" t="n">
-        <v>91883</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588849</v>
+        <v>588925</v>
       </c>
       <c r="R2" t="n">
-        <v>6378218</v>
+        <v>6378093</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,7 +791,7 @@
         <v>119789953</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119790007</v>
+        <v>119790021</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589019</v>
+        <v>588905</v>
       </c>
       <c r="R4" t="n">
-        <v>6377960</v>
+        <v>6378039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119789982</v>
+        <v>119790007</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589045</v>
+        <v>589019</v>
       </c>
       <c r="R5" t="n">
-        <v>6377954</v>
+        <v>6377960</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119789941</v>
+        <v>119790089</v>
       </c>
       <c r="B6" t="n">
-        <v>90582</v>
+        <v>90600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588925</v>
+        <v>588906</v>
       </c>
       <c r="R6" t="n">
-        <v>6378093</v>
+        <v>6378054</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,6 +1224,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1245,7 +1246,7 @@
         <v>119789969</v>
       </c>
       <c r="B7" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1348,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119790043</v>
+        <v>119789982</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1361,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1386,13 +1387,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588905</v>
+        <v>589045</v>
       </c>
       <c r="R8" t="n">
-        <v>6378039</v>
+        <v>6377954</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,6 +1444,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1462,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119790021</v>
+        <v>119789934</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>91901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,35 +1475,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1513,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588905</v>
+        <v>588849</v>
       </c>
       <c r="R9" t="n">
-        <v>6378039</v>
+        <v>6378218</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1558,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119790089</v>
+        <v>119790043</v>
       </c>
       <c r="B10" t="n">
-        <v>90582</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1614,12 +1614,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1627,13 +1628,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588906</v>
+        <v>588905</v>
       </c>
       <c r="R10" t="n">
-        <v>6378054</v>
+        <v>6378039</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1671,7 +1672,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119895576</v>
+        <v>119894515</v>
       </c>
       <c r="B11" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,14 +1726,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588943</v>
+        <v>589143</v>
       </c>
       <c r="R11" t="n">
-        <v>6378050</v>
+        <v>6378011</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119894264</v>
+        <v>119895576</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>94704</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,41 +1814,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589103</v>
+        <v>588943</v>
       </c>
       <c r="R12" t="n">
-        <v>6377996</v>
+        <v>6378050</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119895525</v>
+        <v>119895883</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>94704</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,43 +1930,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588912</v>
+        <v>589100</v>
       </c>
       <c r="R13" t="n">
-        <v>6378042</v>
+        <v>6378008</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1998,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119895508</v>
+        <v>119895306</v>
       </c>
       <c r="B14" t="n">
-        <v>91832</v>
+        <v>90600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,45 +2042,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588905</v>
+        <v>588929</v>
       </c>
       <c r="R14" t="n">
-        <v>6378030</v>
+        <v>6378092</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2121,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2111,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,7 +2120,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2159,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119895685</v>
+        <v>119895508</v>
       </c>
       <c r="B15" t="n">
-        <v>94681</v>
+        <v>91850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,25 +2150,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2199,16 +2178,18 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589007</v>
+        <v>588905</v>
       </c>
       <c r="R15" t="n">
         <v>6378030</v>
@@ -2243,7 +2224,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2234,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,6 +2243,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2280,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119895883</v>
+        <v>119894264</v>
       </c>
       <c r="B16" t="n">
-        <v>94681</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,25 +2274,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,13 +2302,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589100</v>
+        <v>589103</v>
       </c>
       <c r="R16" t="n">
-        <v>6378008</v>
+        <v>6377996</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,7 +2337,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2347,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119895405</v>
+        <v>119895685</v>
       </c>
       <c r="B17" t="n">
-        <v>90582</v>
+        <v>94704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,41 +2386,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588908</v>
+        <v>589007</v>
       </c>
       <c r="R17" t="n">
-        <v>6378060</v>
+        <v>6378030</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2467,7 +2458,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2468,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119895306</v>
+        <v>119895405</v>
       </c>
       <c r="B18" t="n">
-        <v>90582</v>
+        <v>90600</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,13 +2535,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588929</v>
+        <v>588908</v>
       </c>
       <c r="R18" t="n">
-        <v>6378092</v>
+        <v>6378060</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2579,7 +2570,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2589,7 +2580,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119894515</v>
+        <v>119895525</v>
       </c>
       <c r="B19" t="n">
-        <v>94681</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2632,34 +2623,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589143</v>
+        <v>588912</v>
       </c>
       <c r="R19" t="n">
-        <v>6378011</v>
+        <v>6378042</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,7 +2731,7 @@
         <v>119894432</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119950873</v>
+        <v>119951014</v>
       </c>
       <c r="B21" t="n">
-        <v>79144</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,24 +2861,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2888,10 +2892,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588864</v>
+        <v>589030</v>
       </c>
       <c r="R21" t="n">
-        <v>6378060</v>
+        <v>6377964</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2961,10 +2965,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119951016</v>
+        <v>119950915</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2977,28 +2981,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589034</v>
+        <v>588998</v>
       </c>
       <c r="R22" t="n">
-        <v>6377962</v>
+        <v>6377948</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3084,7 +3084,7 @@
         <v>119951024</v>
       </c>
       <c r="B23" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119950865</v>
+        <v>119950738</v>
       </c>
       <c r="B24" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588863</v>
+        <v>588797</v>
       </c>
       <c r="R24" t="n">
-        <v>6378059</v>
+        <v>6378202</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3313,10 +3313,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119951000</v>
+        <v>119950718</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>94704</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3325,34 +3325,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3360,10 +3357,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588820</v>
+        <v>588792</v>
       </c>
       <c r="R25" t="n">
-        <v>6378230</v>
+        <v>6378207</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3433,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119951014</v>
+        <v>119950884</v>
       </c>
       <c r="B26" t="n">
-        <v>91832</v>
+        <v>90600</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3449,21 +3446,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3480,10 +3477,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589030</v>
+        <v>588870</v>
       </c>
       <c r="R26" t="n">
-        <v>6377964</v>
+        <v>6377977</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3553,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119950713</v>
+        <v>119951000</v>
       </c>
       <c r="B27" t="n">
-        <v>79144</v>
+        <v>91902</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3569,24 +3566,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3596,10 +3597,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588800</v>
+        <v>588820</v>
       </c>
       <c r="R27" t="n">
-        <v>6378217</v>
+        <v>6378230</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3669,10 +3670,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119951055</v>
+        <v>119951016</v>
       </c>
       <c r="B28" t="n">
-        <v>79144</v>
+        <v>91850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3685,24 +3686,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3712,10 +3717,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588879</v>
+        <v>589034</v>
       </c>
       <c r="R28" t="n">
-        <v>6377973</v>
+        <v>6377962</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3785,10 +3790,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950796</v>
+        <v>119950815</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
+        <v>94704</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3797,30 +3802,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3828,10 +3834,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588888</v>
+        <v>588881</v>
       </c>
       <c r="R29" t="n">
-        <v>6378207</v>
+        <v>6378203</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3901,10 +3907,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950738</v>
+        <v>119951055</v>
       </c>
       <c r="B30" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3944,10 +3950,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588797</v>
+        <v>588879</v>
       </c>
       <c r="R30" t="n">
-        <v>6378202</v>
+        <v>6377973</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4017,10 +4023,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950786</v>
+        <v>119950865</v>
       </c>
       <c r="B31" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4060,10 +4066,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588866</v>
+        <v>588863</v>
       </c>
       <c r="R31" t="n">
-        <v>6378218</v>
+        <v>6378059</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4133,10 +4139,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950815</v>
+        <v>119950796</v>
       </c>
       <c r="B32" t="n">
-        <v>94681</v>
+        <v>79160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4145,31 +4151,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4177,10 +4182,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588881</v>
+        <v>588888</v>
       </c>
       <c r="R32" t="n">
-        <v>6378203</v>
+        <v>6378207</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4250,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950884</v>
+        <v>119950809</v>
       </c>
       <c r="B33" t="n">
-        <v>90582</v>
+        <v>79160</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4266,28 +4271,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4297,10 +4298,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588870</v>
+        <v>588881</v>
       </c>
       <c r="R33" t="n">
-        <v>6377977</v>
+        <v>6378203</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4370,10 +4371,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950915</v>
+        <v>119950729</v>
       </c>
       <c r="B34" t="n">
-        <v>79144</v>
+        <v>5485</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4386,26 +4387,32 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4413,10 +4420,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588998</v>
+        <v>588786</v>
       </c>
       <c r="R34" t="n">
-        <v>6377948</v>
+        <v>6378207</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4486,10 +4493,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950823</v>
+        <v>119950873</v>
       </c>
       <c r="B35" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4529,10 +4536,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588879</v>
+        <v>588864</v>
       </c>
       <c r="R35" t="n">
-        <v>6378129</v>
+        <v>6378060</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4602,10 +4609,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119950729</v>
+        <v>119950713</v>
       </c>
       <c r="B36" t="n">
-        <v>5485</v>
+        <v>79160</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4618,32 +4625,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4651,10 +4652,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588786</v>
+        <v>588800</v>
       </c>
       <c r="R36" t="n">
-        <v>6378207</v>
+        <v>6378217</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4724,10 +4725,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119950809</v>
+        <v>119950786</v>
       </c>
       <c r="B37" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4767,10 +4768,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588881</v>
+        <v>588866</v>
       </c>
       <c r="R37" t="n">
-        <v>6378203</v>
+        <v>6378218</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4840,10 +4841,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119950718</v>
+        <v>119950823</v>
       </c>
       <c r="B38" t="n">
-        <v>94681</v>
+        <v>79160</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4852,31 +4853,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588792</v>
+        <v>588879</v>
       </c>
       <c r="R38" t="n">
-        <v>6378207</v>
+        <v>6378129</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -2607,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119895525</v>
+        <v>119894432</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,50 +2619,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588912</v>
+        <v>589148</v>
       </c>
       <c r="R19" t="n">
-        <v>6378042</v>
+        <v>6378016</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2691,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2701,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119894432</v>
+        <v>119895525</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2740,46 +2736,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589148</v>
+        <v>588912</v>
       </c>
       <c r="R20" t="n">
-        <v>6378016</v>
+        <v>6378042</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119789941</v>
+        <v>119790043</v>
       </c>
       <c r="B2" t="n">
-        <v>90600</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,12 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588925</v>
+        <v>588905</v>
       </c>
       <c r="R2" t="n">
-        <v>6378093</v>
+        <v>6378039</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -788,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119789953</v>
+        <v>119789934</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,7 +829,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -839,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588908</v>
+        <v>588849</v>
       </c>
       <c r="R3" t="n">
-        <v>6378028</v>
+        <v>6378218</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119790021</v>
+        <v>119789982</v>
       </c>
       <c r="B4" t="n">
         <v>91858</v>
@@ -936,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588905</v>
+        <v>589045</v>
       </c>
       <c r="R4" t="n">
-        <v>6378039</v>
+        <v>6377954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119790007</v>
+        <v>119789969</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,34 +1032,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589019</v>
+        <v>589092</v>
       </c>
       <c r="R5" t="n">
-        <v>6377960</v>
+        <v>6377970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1243,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119789969</v>
+        <v>119789953</v>
       </c>
       <c r="B7" t="n">
-        <v>94704</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,27 +1252,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589092</v>
+        <v>588908</v>
       </c>
       <c r="R7" t="n">
-        <v>6377970</v>
+        <v>6378028</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119789982</v>
+        <v>119790007</v>
       </c>
       <c r="B8" t="n">
         <v>91858</v>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589045</v>
+        <v>589019</v>
       </c>
       <c r="R8" t="n">
-        <v>6377954</v>
+        <v>6377960</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119789934</v>
+        <v>119789941</v>
       </c>
       <c r="B9" t="n">
-        <v>91901</v>
+        <v>90600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1479,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588849</v>
+        <v>588925</v>
       </c>
       <c r="R9" t="n">
-        <v>6378218</v>
+        <v>6378093</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119790043</v>
+        <v>119790021</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,39 +1588,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1634,7 +1633,7 @@
         <v>6378039</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1672,6 +1671,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119894515</v>
+        <v>119895525</v>
       </c>
       <c r="B11" t="n">
-        <v>94704</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,34 +1706,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589143</v>
+        <v>588912</v>
       </c>
       <c r="R11" t="n">
-        <v>6378011</v>
+        <v>6378042</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1765,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1784,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119895576</v>
+        <v>119895306</v>
       </c>
       <c r="B12" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,25 +1823,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588943</v>
+        <v>588929</v>
       </c>
       <c r="R12" t="n">
-        <v>6378050</v>
+        <v>6378092</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1877,7 +1886,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1896,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119895883</v>
+        <v>119894264</v>
       </c>
       <c r="B13" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,25 +1935,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1954,13 +1963,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589100</v>
+        <v>589103</v>
       </c>
       <c r="R13" t="n">
-        <v>6378008</v>
+        <v>6377996</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,7 +2035,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119895306</v>
+        <v>119895405</v>
       </c>
       <c r="B14" t="n">
         <v>90600</v>
@@ -2066,13 +2075,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588929</v>
+        <v>588908</v>
       </c>
       <c r="R14" t="n">
-        <v>6378092</v>
+        <v>6378060</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,7 +2110,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2111,7 +2120,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119895508</v>
+        <v>119895883</v>
       </c>
       <c r="B15" t="n">
-        <v>91850</v>
+        <v>94704</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2150,49 +2159,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588905</v>
+        <v>589100</v>
       </c>
       <c r="R15" t="n">
-        <v>6378030</v>
+        <v>6378008</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2224,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2234,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,7 +2241,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2262,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119894264</v>
+        <v>119895576</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,41 +2271,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589103</v>
+        <v>588943</v>
       </c>
       <c r="R16" t="n">
-        <v>6377996</v>
+        <v>6378050</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2337,7 +2334,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2347,7 +2344,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2495,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119895405</v>
+        <v>119895508</v>
       </c>
       <c r="B18" t="n">
-        <v>90600</v>
+        <v>91850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,37 +2508,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588908</v>
+        <v>588905</v>
       </c>
       <c r="R18" t="n">
-        <v>6378060</v>
+        <v>6378030</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2570,7 +2578,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,7 +2588,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,6 +2597,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2724,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119895525</v>
+        <v>119894515</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2740,43 +2749,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588912</v>
+        <v>589143</v>
       </c>
       <c r="R20" t="n">
-        <v>6378042</v>
+        <v>6378011</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119951014</v>
+        <v>119950796</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,28 +2861,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2892,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589030</v>
+        <v>588888</v>
       </c>
       <c r="R21" t="n">
-        <v>6377964</v>
+        <v>6378207</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2965,7 +2961,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119950915</v>
+        <v>119950873</v>
       </c>
       <c r="B22" t="n">
         <v>79160</v>
@@ -3008,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588998</v>
+        <v>588864</v>
       </c>
       <c r="R22" t="n">
-        <v>6377948</v>
+        <v>6378060</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3081,7 +3077,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119951024</v>
+        <v>119950809</v>
       </c>
       <c r="B23" t="n">
         <v>79160</v>
@@ -3124,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588886</v>
+        <v>588881</v>
       </c>
       <c r="R23" t="n">
-        <v>6377979</v>
+        <v>6378203</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3313,10 +3309,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119950718</v>
+        <v>119951055</v>
       </c>
       <c r="B25" t="n">
-        <v>94704</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3325,31 +3321,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3357,10 +3352,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588792</v>
+        <v>588879</v>
       </c>
       <c r="R25" t="n">
-        <v>6378207</v>
+        <v>6377973</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3430,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119950884</v>
+        <v>119950815</v>
       </c>
       <c r="B26" t="n">
-        <v>90600</v>
+        <v>94704</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3442,34 +3437,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3477,10 +3469,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588870</v>
+        <v>588881</v>
       </c>
       <c r="R26" t="n">
-        <v>6377977</v>
+        <v>6378203</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3550,10 +3542,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119951000</v>
+        <v>119950884</v>
       </c>
       <c r="B27" t="n">
-        <v>91902</v>
+        <v>90600</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,26 +3558,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3597,10 +3589,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588820</v>
+        <v>588870</v>
       </c>
       <c r="R27" t="n">
-        <v>6378230</v>
+        <v>6377977</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3670,10 +3662,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119951016</v>
+        <v>119950915</v>
       </c>
       <c r="B28" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3686,28 +3678,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3717,10 +3705,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589034</v>
+        <v>588998</v>
       </c>
       <c r="R28" t="n">
-        <v>6377962</v>
+        <v>6377948</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3790,10 +3778,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950815</v>
+        <v>119951016</v>
       </c>
       <c r="B29" t="n">
-        <v>94704</v>
+        <v>91850</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3802,31 +3790,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3834,10 +3825,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588881</v>
+        <v>589034</v>
       </c>
       <c r="R29" t="n">
-        <v>6378203</v>
+        <v>6377962</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3907,10 +3898,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119951055</v>
+        <v>119951000</v>
       </c>
       <c r="B30" t="n">
-        <v>79160</v>
+        <v>91902</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3923,24 +3914,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3950,10 +3945,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588879</v>
+        <v>588820</v>
       </c>
       <c r="R30" t="n">
-        <v>6377973</v>
+        <v>6378230</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4023,7 +4018,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950865</v>
+        <v>119950823</v>
       </c>
       <c r="B31" t="n">
         <v>79160</v>
@@ -4066,10 +4061,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588863</v>
+        <v>588879</v>
       </c>
       <c r="R31" t="n">
-        <v>6378059</v>
+        <v>6378129</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4139,10 +4134,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950796</v>
+        <v>119950729</v>
       </c>
       <c r="B32" t="n">
-        <v>79160</v>
+        <v>5485</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4155,26 +4150,32 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4182,7 +4183,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588888</v>
+        <v>588786</v>
       </c>
       <c r="R32" t="n">
         <v>6378207</v>
@@ -4255,7 +4256,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950809</v>
+        <v>119951024</v>
       </c>
       <c r="B33" t="n">
         <v>79160</v>
@@ -4298,10 +4299,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588881</v>
+        <v>588886</v>
       </c>
       <c r="R33" t="n">
-        <v>6378203</v>
+        <v>6377979</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4371,10 +4372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950729</v>
+        <v>119950865</v>
       </c>
       <c r="B34" t="n">
-        <v>5485</v>
+        <v>79160</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4387,32 +4388,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4420,10 +4415,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588786</v>
+        <v>588863</v>
       </c>
       <c r="R34" t="n">
-        <v>6378207</v>
+        <v>6378059</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4493,10 +4488,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950873</v>
+        <v>119950718</v>
       </c>
       <c r="B35" t="n">
-        <v>79160</v>
+        <v>94704</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4505,30 +4500,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4536,10 +4532,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588864</v>
+        <v>588792</v>
       </c>
       <c r="R35" t="n">
-        <v>6378060</v>
+        <v>6378207</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4609,10 +4605,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119950713</v>
+        <v>119951014</v>
       </c>
       <c r="B36" t="n">
-        <v>79160</v>
+        <v>91850</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4625,24 +4621,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588800</v>
+        <v>589030</v>
       </c>
       <c r="R36" t="n">
-        <v>6378217</v>
+        <v>6377964</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119950786</v>
+        <v>119950713</v>
       </c>
       <c r="B37" t="n">
         <v>79160</v>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588866</v>
+        <v>588800</v>
       </c>
       <c r="R37" t="n">
-        <v>6378218</v>
+        <v>6378217</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119950823</v>
+        <v>119950786</v>
       </c>
       <c r="B38" t="n">
         <v>79160</v>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588879</v>
+        <v>588866</v>
       </c>
       <c r="R38" t="n">
-        <v>6378129</v>
+        <v>6378218</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -2961,7 +2961,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119950873</v>
+        <v>119950809</v>
       </c>
       <c r="B22" t="n">
         <v>79160</v>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588864</v>
+        <v>588881</v>
       </c>
       <c r="R22" t="n">
-        <v>6378060</v>
+        <v>6378203</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3077,7 +3077,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950809</v>
+        <v>119950873</v>
       </c>
       <c r="B23" t="n">
         <v>79160</v>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588881</v>
+        <v>588864</v>
       </c>
       <c r="R23" t="n">
-        <v>6378203</v>
+        <v>6378060</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119895525</v>
+        <v>119895508</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1702,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1733,16 +1733,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588912</v>
+        <v>588905</v>
       </c>
       <c r="R11" t="n">
-        <v>6378042</v>
+        <v>6378030</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1774,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,6 +1795,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1811,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119895306</v>
+        <v>119895883</v>
       </c>
       <c r="B12" t="n">
-        <v>90600</v>
+        <v>94704</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,38 +1826,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588929</v>
+        <v>589100</v>
       </c>
       <c r="R12" t="n">
-        <v>6378092</v>
+        <v>6378008</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1886,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119894264</v>
+        <v>119895576</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,41 +1938,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589103</v>
+        <v>588943</v>
       </c>
       <c r="R13" t="n">
-        <v>6377996</v>
+        <v>6378050</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1998,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119895405</v>
+        <v>119895525</v>
       </c>
       <c r="B14" t="n">
-        <v>90600</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,41 +2050,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588908</v>
+        <v>588912</v>
       </c>
       <c r="R14" t="n">
-        <v>6378060</v>
+        <v>6378042</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2110,7 +2122,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2120,7 +2132,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,7 +2159,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119895883</v>
+        <v>119894515</v>
       </c>
       <c r="B15" t="n">
         <v>94704</v>
@@ -2187,10 +2199,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589100</v>
+        <v>589143</v>
       </c>
       <c r="R15" t="n">
-        <v>6378008</v>
+        <v>6378011</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2222,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119895576</v>
+        <v>119894432</v>
       </c>
       <c r="B16" t="n">
-        <v>94704</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2271,41 +2283,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588943</v>
+        <v>589148</v>
       </c>
       <c r="R16" t="n">
-        <v>6378050</v>
+        <v>6378016</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2334,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2344,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119895685</v>
+        <v>119895405</v>
       </c>
       <c r="B17" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2383,50 +2400,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589007</v>
+        <v>588908</v>
       </c>
       <c r="R17" t="n">
-        <v>6378030</v>
+        <v>6378060</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119895508</v>
+        <v>119894264</v>
       </c>
       <c r="B18" t="n">
-        <v>91850</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,48 +2516,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588905</v>
+        <v>589103</v>
       </c>
       <c r="R18" t="n">
-        <v>6378030</v>
+        <v>6377996</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2578,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2588,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,7 +2594,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2616,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119894432</v>
+        <v>119895306</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>90600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2632,42 +2628,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589148</v>
+        <v>588929</v>
       </c>
       <c r="R19" t="n">
-        <v>6378016</v>
+        <v>6378092</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2696,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,7 +2724,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119894515</v>
+        <v>119895685</v>
       </c>
       <c r="B20" t="n">
         <v>94704</v>
@@ -2766,17 +2757,26 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589143</v>
+        <v>589007</v>
       </c>
       <c r="R20" t="n">
-        <v>6378011</v>
+        <v>6378030</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,7 +2845,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119950796</v>
+        <v>119950865</v>
       </c>
       <c r="B21" t="n">
         <v>79160</v>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588888</v>
+        <v>588863</v>
       </c>
       <c r="R21" t="n">
-        <v>6378207</v>
+        <v>6378059</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119950809</v>
+        <v>119950796</v>
       </c>
       <c r="B22" t="n">
         <v>79160</v>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588881</v>
+        <v>588888</v>
       </c>
       <c r="R22" t="n">
-        <v>6378203</v>
+        <v>6378207</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119950738</v>
+        <v>119951014</v>
       </c>
       <c r="B24" t="n">
-        <v>79160</v>
+        <v>91850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3209,24 +3209,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3236,10 +3240,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588797</v>
+        <v>589030</v>
       </c>
       <c r="R24" t="n">
-        <v>6378202</v>
+        <v>6377964</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3309,10 +3313,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119951055</v>
+        <v>119950884</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>90600</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3325,24 +3329,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3352,10 +3360,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588879</v>
+        <v>588870</v>
       </c>
       <c r="R25" t="n">
-        <v>6377973</v>
+        <v>6377977</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3425,10 +3433,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119950815</v>
+        <v>119951055</v>
       </c>
       <c r="B26" t="n">
-        <v>94704</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3437,31 +3445,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3469,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588881</v>
+        <v>588879</v>
       </c>
       <c r="R26" t="n">
-        <v>6378203</v>
+        <v>6377973</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3542,10 +3549,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119950884</v>
+        <v>119950815</v>
       </c>
       <c r="B27" t="n">
-        <v>90600</v>
+        <v>94704</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3554,34 +3561,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3589,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588870</v>
+        <v>588881</v>
       </c>
       <c r="R27" t="n">
-        <v>6377977</v>
+        <v>6378203</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3662,10 +3666,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119950915</v>
+        <v>119951016</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
+        <v>91850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3678,24 +3682,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3705,10 +3713,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588998</v>
+        <v>589034</v>
       </c>
       <c r="R28" t="n">
-        <v>6377948</v>
+        <v>6377962</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3778,10 +3786,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119951016</v>
+        <v>119950729</v>
       </c>
       <c r="B29" t="n">
-        <v>91850</v>
+        <v>5485</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3794,21 +3802,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>101410</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3818,6 +3826,8 @@
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3825,10 +3835,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589034</v>
+        <v>588786</v>
       </c>
       <c r="R29" t="n">
-        <v>6377962</v>
+        <v>6378207</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3898,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119951000</v>
+        <v>119950738</v>
       </c>
       <c r="B30" t="n">
-        <v>91902</v>
+        <v>79160</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3914,28 +3924,24 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3945,10 +3951,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588820</v>
+        <v>588797</v>
       </c>
       <c r="R30" t="n">
-        <v>6378230</v>
+        <v>6378202</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4134,10 +4140,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950729</v>
+        <v>119951000</v>
       </c>
       <c r="B32" t="n">
-        <v>5485</v>
+        <v>91902</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4150,32 +4156,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>101410</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4183,10 +4187,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588786</v>
+        <v>588820</v>
       </c>
       <c r="R32" t="n">
-        <v>6378207</v>
+        <v>6378230</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4256,7 +4260,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119951024</v>
+        <v>119950786</v>
       </c>
       <c r="B33" t="n">
         <v>79160</v>
@@ -4299,10 +4303,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588886</v>
+        <v>588866</v>
       </c>
       <c r="R33" t="n">
-        <v>6377979</v>
+        <v>6378218</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4372,10 +4376,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950865</v>
+        <v>119950718</v>
       </c>
       <c r="B34" t="n">
-        <v>79160</v>
+        <v>94704</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4384,30 +4388,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4415,10 +4420,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588863</v>
+        <v>588792</v>
       </c>
       <c r="R34" t="n">
-        <v>6378059</v>
+        <v>6378207</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4488,10 +4493,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950718</v>
+        <v>119950915</v>
       </c>
       <c r="B35" t="n">
-        <v>94704</v>
+        <v>79160</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4500,31 +4505,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4532,10 +4536,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588792</v>
+        <v>588998</v>
       </c>
       <c r="R35" t="n">
-        <v>6378207</v>
+        <v>6377948</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4605,10 +4609,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119951014</v>
+        <v>119950713</v>
       </c>
       <c r="B36" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4621,28 +4625,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589030</v>
+        <v>588800</v>
       </c>
       <c r="R36" t="n">
-        <v>6377964</v>
+        <v>6378217</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119950713</v>
+        <v>119950809</v>
       </c>
       <c r="B37" t="n">
         <v>79160</v>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588800</v>
+        <v>588881</v>
       </c>
       <c r="R37" t="n">
-        <v>6378217</v>
+        <v>6378203</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119950786</v>
+        <v>119951024</v>
       </c>
       <c r="B38" t="n">
         <v>79160</v>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588866</v>
+        <v>588886</v>
       </c>
       <c r="R38" t="n">
-        <v>6378218</v>
+        <v>6377979</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119895405</v>
+        <v>119894264</v>
       </c>
       <c r="B17" t="n">
-        <v>90600</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,37 +2404,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588908</v>
+        <v>589103</v>
       </c>
       <c r="R17" t="n">
-        <v>6378060</v>
+        <v>6377996</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119894264</v>
+        <v>119895405</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>90600</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,37 +2516,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589103</v>
+        <v>588908</v>
       </c>
       <c r="R18" t="n">
-        <v>6377996</v>
+        <v>6378060</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119895508</v>
+        <v>119895685</v>
       </c>
       <c r="B11" t="n">
-        <v>91850</v>
+        <v>94704</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1702,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1730,18 +1730,16 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588905</v>
+        <v>589007</v>
       </c>
       <c r="R11" t="n">
         <v>6378030</v>
@@ -1776,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1784,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1793,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1814,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119895883</v>
+        <v>119895508</v>
       </c>
       <c r="B12" t="n">
-        <v>94704</v>
+        <v>91850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,38 +1823,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589100</v>
+        <v>588905</v>
       </c>
       <c r="R12" t="n">
-        <v>6378008</v>
+        <v>6378030</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1889,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,6 +1916,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1926,7 +1935,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119895576</v>
+        <v>119894515</v>
       </c>
       <c r="B13" t="n">
         <v>94704</v>
@@ -1962,14 +1971,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588943</v>
+        <v>589143</v>
       </c>
       <c r="R13" t="n">
-        <v>6378050</v>
+        <v>6378011</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2001,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119895525</v>
+        <v>119895576</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,43 +2063,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588912</v>
+        <v>588943</v>
       </c>
       <c r="R14" t="n">
-        <v>6378042</v>
+        <v>6378050</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119894515</v>
+        <v>119894432</v>
       </c>
       <c r="B15" t="n">
-        <v>94704</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,41 +2171,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589143</v>
+        <v>589148</v>
       </c>
       <c r="R15" t="n">
-        <v>6378011</v>
+        <v>6378016</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2234,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119894432</v>
+        <v>119894264</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,39 +2292,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589148</v>
+        <v>589103</v>
       </c>
       <c r="R16" t="n">
-        <v>6378016</v>
+        <v>6377996</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119894264</v>
+        <v>119895883</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,25 +2400,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589103</v>
+        <v>589100</v>
       </c>
       <c r="R17" t="n">
-        <v>6377996</v>
+        <v>6378008</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119895405</v>
+        <v>119895525</v>
       </c>
       <c r="B18" t="n">
-        <v>90600</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,41 +2512,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588908</v>
+        <v>588912</v>
       </c>
       <c r="R18" t="n">
-        <v>6378060</v>
+        <v>6378042</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2575,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2724,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119895685</v>
+        <v>119895405</v>
       </c>
       <c r="B20" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,50 +2745,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589007</v>
+        <v>588908</v>
       </c>
       <c r="R20" t="n">
-        <v>6378030</v>
+        <v>6378060</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119950865</v>
+        <v>119951000</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>91902</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,24 +2861,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2888,10 +2892,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588863</v>
+        <v>588820</v>
       </c>
       <c r="R21" t="n">
-        <v>6378059</v>
+        <v>6378230</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2961,10 +2965,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119950796</v>
+        <v>119950815</v>
       </c>
       <c r="B22" t="n">
-        <v>79160</v>
+        <v>94704</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2973,30 +2977,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3004,10 +3009,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588888</v>
+        <v>588881</v>
       </c>
       <c r="R22" t="n">
-        <v>6378207</v>
+        <v>6378203</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3077,7 +3082,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950873</v>
+        <v>119950796</v>
       </c>
       <c r="B23" t="n">
         <v>79160</v>
@@ -3120,10 +3125,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588864</v>
+        <v>588888</v>
       </c>
       <c r="R23" t="n">
-        <v>6378060</v>
+        <v>6378207</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3193,10 +3198,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119951014</v>
+        <v>119950718</v>
       </c>
       <c r="B24" t="n">
-        <v>91850</v>
+        <v>94704</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3205,34 +3210,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3240,10 +3242,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589030</v>
+        <v>588792</v>
       </c>
       <c r="R24" t="n">
-        <v>6377964</v>
+        <v>6378207</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3313,10 +3315,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119950884</v>
+        <v>119950915</v>
       </c>
       <c r="B25" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3329,28 +3331,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3360,10 +3358,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588870</v>
+        <v>588998</v>
       </c>
       <c r="R25" t="n">
-        <v>6377977</v>
+        <v>6377948</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3433,10 +3431,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119951055</v>
+        <v>119951014</v>
       </c>
       <c r="B26" t="n">
-        <v>79160</v>
+        <v>91850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3449,24 +3447,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3476,10 +3478,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588879</v>
+        <v>589030</v>
       </c>
       <c r="R26" t="n">
-        <v>6377973</v>
+        <v>6377964</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3549,10 +3551,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119950815</v>
+        <v>119950865</v>
       </c>
       <c r="B27" t="n">
-        <v>94704</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3561,31 +3563,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3593,10 +3594,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588881</v>
+        <v>588863</v>
       </c>
       <c r="R27" t="n">
-        <v>6378203</v>
+        <v>6378059</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3666,10 +3667,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119951016</v>
+        <v>119950786</v>
       </c>
       <c r="B28" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3682,28 +3683,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3713,10 +3710,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589034</v>
+        <v>588866</v>
       </c>
       <c r="R28" t="n">
-        <v>6377962</v>
+        <v>6378218</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3786,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950729</v>
+        <v>119950873</v>
       </c>
       <c r="B29" t="n">
-        <v>5485</v>
+        <v>79160</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3802,32 +3799,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3835,10 +3826,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588786</v>
+        <v>588864</v>
       </c>
       <c r="R29" t="n">
-        <v>6378207</v>
+        <v>6378060</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4024,7 +4015,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950823</v>
+        <v>119950713</v>
       </c>
       <c r="B31" t="n">
         <v>79160</v>
@@ -4067,10 +4058,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588879</v>
+        <v>588800</v>
       </c>
       <c r="R31" t="n">
-        <v>6378129</v>
+        <v>6378217</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4140,10 +4131,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119951000</v>
+        <v>119951024</v>
       </c>
       <c r="B32" t="n">
-        <v>91902</v>
+        <v>79160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4156,28 +4147,24 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -4187,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588820</v>
+        <v>588886</v>
       </c>
       <c r="R32" t="n">
-        <v>6378230</v>
+        <v>6377979</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4260,10 +4247,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950786</v>
+        <v>119950729</v>
       </c>
       <c r="B33" t="n">
-        <v>79160</v>
+        <v>5485</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4276,26 +4263,32 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4303,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588866</v>
+        <v>588786</v>
       </c>
       <c r="R33" t="n">
-        <v>6378218</v>
+        <v>6378207</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4376,10 +4369,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950718</v>
+        <v>119950884</v>
       </c>
       <c r="B34" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4388,31 +4381,34 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4420,10 +4416,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588792</v>
+        <v>588870</v>
       </c>
       <c r="R34" t="n">
-        <v>6378207</v>
+        <v>6377977</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4493,7 +4489,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950915</v>
+        <v>119950809</v>
       </c>
       <c r="B35" t="n">
         <v>79160</v>
@@ -4536,10 +4532,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588998</v>
+        <v>588881</v>
       </c>
       <c r="R35" t="n">
-        <v>6377948</v>
+        <v>6378203</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4609,10 +4605,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119950713</v>
+        <v>119951016</v>
       </c>
       <c r="B36" t="n">
-        <v>79160</v>
+        <v>91850</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4625,24 +4621,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588800</v>
+        <v>589034</v>
       </c>
       <c r="R36" t="n">
-        <v>6378217</v>
+        <v>6377962</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119950809</v>
+        <v>119951055</v>
       </c>
       <c r="B37" t="n">
         <v>79160</v>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588881</v>
+        <v>588879</v>
       </c>
       <c r="R37" t="n">
-        <v>6378203</v>
+        <v>6377973</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119951024</v>
+        <v>119950823</v>
       </c>
       <c r="B38" t="n">
         <v>79160</v>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588886</v>
+        <v>588879</v>
       </c>
       <c r="R38" t="n">
-        <v>6377979</v>
+        <v>6378129</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119895685</v>
+        <v>119894264</v>
       </c>
       <c r="B11" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,50 +1702,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589007</v>
+        <v>589103</v>
       </c>
       <c r="R11" t="n">
-        <v>6378030</v>
+        <v>6377996</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119895508</v>
+        <v>119895405</v>
       </c>
       <c r="B12" t="n">
-        <v>91850</v>
+        <v>90600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,48 +1818,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588905</v>
+        <v>588908</v>
       </c>
       <c r="R12" t="n">
-        <v>6378030</v>
+        <v>6378060</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1896,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1935,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119894515</v>
+        <v>119895525</v>
       </c>
       <c r="B13" t="n">
-        <v>94704</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,34 +1930,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589143</v>
+        <v>588912</v>
       </c>
       <c r="R13" t="n">
-        <v>6378011</v>
+        <v>6378042</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2010,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119895576</v>
+        <v>119895306</v>
       </c>
       <c r="B14" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,25 +2047,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2087,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588943</v>
+        <v>588929</v>
       </c>
       <c r="R14" t="n">
-        <v>6378050</v>
+        <v>6378092</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2122,7 +2110,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2132,7 +2120,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119894432</v>
+        <v>119895508</v>
       </c>
       <c r="B15" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,42 +2163,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bastkärr, Bastkärr, Sm</t>
+          <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589148</v>
+        <v>588905</v>
       </c>
       <c r="R15" t="n">
-        <v>6378016</v>
+        <v>6378030</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2239,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,6 +2252,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2276,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119894264</v>
+        <v>119895883</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,25 +2283,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,13 +2311,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589103</v>
+        <v>589100</v>
       </c>
       <c r="R16" t="n">
-        <v>6377996</v>
+        <v>6378008</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2351,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119895883</v>
+        <v>119894432</v>
       </c>
       <c r="B17" t="n">
-        <v>94704</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,41 +2395,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589100</v>
+        <v>589148</v>
       </c>
       <c r="R17" t="n">
-        <v>6378008</v>
+        <v>6378016</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119895525</v>
+        <v>119894515</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,43 +2516,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Melekärret, Melekärret, Sm</t>
+          <t>Bastkärr, Bastkärr, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588912</v>
+        <v>589143</v>
       </c>
       <c r="R18" t="n">
-        <v>6378042</v>
+        <v>6378011</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2584,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119895306</v>
+        <v>119895685</v>
       </c>
       <c r="B19" t="n">
-        <v>90600</v>
+        <v>94704</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,38 +2624,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Melekärret, Melekärret, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588929</v>
+        <v>589007</v>
       </c>
       <c r="R19" t="n">
-        <v>6378092</v>
+        <v>6378030</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119895405</v>
+        <v>119895576</v>
       </c>
       <c r="B20" t="n">
-        <v>90600</v>
+        <v>94704</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,25 +2745,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2773,13 +2773,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588908</v>
+        <v>588943</v>
       </c>
       <c r="R20" t="n">
-        <v>6378060</v>
+        <v>6378050</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119951000</v>
+        <v>119950823</v>
       </c>
       <c r="B21" t="n">
-        <v>91902</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,28 +2861,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2892,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588820</v>
+        <v>588879</v>
       </c>
       <c r="R21" t="n">
-        <v>6378230</v>
+        <v>6378129</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2965,10 +2961,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119950815</v>
+        <v>119951016</v>
       </c>
       <c r="B22" t="n">
-        <v>94704</v>
+        <v>91850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2977,31 +2973,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3009,10 +3008,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588881</v>
+        <v>589034</v>
       </c>
       <c r="R22" t="n">
-        <v>6378203</v>
+        <v>6377962</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3082,10 +3081,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950796</v>
+        <v>119950729</v>
       </c>
       <c r="B23" t="n">
-        <v>79160</v>
+        <v>5485</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3098,26 +3097,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3125,7 +3130,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588888</v>
+        <v>588786</v>
       </c>
       <c r="R23" t="n">
         <v>6378207</v>
@@ -3431,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119951014</v>
+        <v>119950796</v>
       </c>
       <c r="B26" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3447,28 +3452,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3478,10 +3479,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589030</v>
+        <v>588888</v>
       </c>
       <c r="R26" t="n">
-        <v>6377964</v>
+        <v>6378207</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3551,7 +3552,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119950865</v>
+        <v>119950809</v>
       </c>
       <c r="B27" t="n">
         <v>79160</v>
@@ -3594,10 +3595,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588863</v>
+        <v>588881</v>
       </c>
       <c r="R27" t="n">
-        <v>6378059</v>
+        <v>6378203</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3667,10 +3668,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119950786</v>
+        <v>119950815</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
+        <v>94704</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3679,30 +3680,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3710,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588866</v>
+        <v>588881</v>
       </c>
       <c r="R28" t="n">
-        <v>6378218</v>
+        <v>6378203</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3783,7 +3785,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950873</v>
+        <v>119950738</v>
       </c>
       <c r="B29" t="n">
         <v>79160</v>
@@ -3826,10 +3828,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588864</v>
+        <v>588797</v>
       </c>
       <c r="R29" t="n">
-        <v>6378060</v>
+        <v>6378202</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3899,7 +3901,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950738</v>
+        <v>119950713</v>
       </c>
       <c r="B30" t="n">
         <v>79160</v>
@@ -3942,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588797</v>
+        <v>588800</v>
       </c>
       <c r="R30" t="n">
-        <v>6378202</v>
+        <v>6378217</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4015,10 +4017,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950713</v>
+        <v>119951000</v>
       </c>
       <c r="B31" t="n">
-        <v>79160</v>
+        <v>91902</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4031,24 +4033,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -4058,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588800</v>
+        <v>588820</v>
       </c>
       <c r="R31" t="n">
-        <v>6378217</v>
+        <v>6378230</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4131,7 +4137,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119951024</v>
+        <v>119950873</v>
       </c>
       <c r="B32" t="n">
         <v>79160</v>
@@ -4174,10 +4180,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588886</v>
+        <v>588864</v>
       </c>
       <c r="R32" t="n">
-        <v>6377979</v>
+        <v>6378060</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4247,10 +4253,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950729</v>
+        <v>119950786</v>
       </c>
       <c r="B33" t="n">
-        <v>5485</v>
+        <v>79160</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4263,32 +4269,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588786</v>
+        <v>588866</v>
       </c>
       <c r="R33" t="n">
-        <v>6378207</v>
+        <v>6378218</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4369,10 +4369,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950884</v>
+        <v>119951024</v>
       </c>
       <c r="B34" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4385,28 +4385,24 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4416,10 +4412,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588870</v>
+        <v>588886</v>
       </c>
       <c r="R34" t="n">
-        <v>6377977</v>
+        <v>6377979</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4489,10 +4485,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950809</v>
+        <v>119950884</v>
       </c>
       <c r="B35" t="n">
-        <v>79160</v>
+        <v>90600</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4505,24 +4501,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588881</v>
+        <v>588870</v>
       </c>
       <c r="R35" t="n">
-        <v>6378203</v>
+        <v>6377977</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4605,10 +4605,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119951016</v>
+        <v>119950865</v>
       </c>
       <c r="B36" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4621,28 +4621,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4652,10 +4648,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589034</v>
+        <v>588863</v>
       </c>
       <c r="R36" t="n">
-        <v>6377962</v>
+        <v>6378059</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4841,10 +4837,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119950823</v>
+        <v>119951014</v>
       </c>
       <c r="B38" t="n">
-        <v>79160</v>
+        <v>91850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4857,24 +4853,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588879</v>
+        <v>589030</v>
       </c>
       <c r="R38" t="n">
-        <v>6378129</v>
+        <v>6377964</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -2845,7 +2845,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119950823</v>
+        <v>119951055</v>
       </c>
       <c r="B21" t="n">
         <v>79160</v>
@@ -2891,7 +2891,7 @@
         <v>588879</v>
       </c>
       <c r="R21" t="n">
-        <v>6378129</v>
+        <v>6377973</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119951016</v>
+        <v>119950718</v>
       </c>
       <c r="B22" t="n">
-        <v>91850</v>
+        <v>94704</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2973,34 +2973,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3008,10 +3005,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589034</v>
+        <v>588792</v>
       </c>
       <c r="R22" t="n">
-        <v>6377962</v>
+        <v>6378207</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3081,10 +3078,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950729</v>
+        <v>119950873</v>
       </c>
       <c r="B23" t="n">
-        <v>5485</v>
+        <v>79160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,32 +3094,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3130,10 +3121,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588786</v>
+        <v>588864</v>
       </c>
       <c r="R23" t="n">
-        <v>6378207</v>
+        <v>6378060</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3203,10 +3194,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119950718</v>
+        <v>119950729</v>
       </c>
       <c r="B24" t="n">
-        <v>94704</v>
+        <v>5485</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3215,31 +3206,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>101410</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3247,7 +3243,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588792</v>
+        <v>588786</v>
       </c>
       <c r="R24" t="n">
         <v>6378207</v>
@@ -3320,10 +3316,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119950915</v>
+        <v>119951000</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>91902</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,24 +3332,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588998</v>
+        <v>588820</v>
       </c>
       <c r="R25" t="n">
-        <v>6377948</v>
+        <v>6378230</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119950796</v>
+        <v>119950884</v>
       </c>
       <c r="B26" t="n">
-        <v>79160</v>
+        <v>90600</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,24 +3452,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3479,10 +3483,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588888</v>
+        <v>588870</v>
       </c>
       <c r="R26" t="n">
-        <v>6378207</v>
+        <v>6377977</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3552,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119950809</v>
+        <v>119951016</v>
       </c>
       <c r="B27" t="n">
-        <v>79160</v>
+        <v>91850</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3568,24 +3572,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3595,10 +3603,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588881</v>
+        <v>589034</v>
       </c>
       <c r="R27" t="n">
-        <v>6378203</v>
+        <v>6377962</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3668,10 +3676,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119950815</v>
+        <v>119950738</v>
       </c>
       <c r="B28" t="n">
-        <v>94704</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,31 +3688,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3712,10 +3719,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588881</v>
+        <v>588797</v>
       </c>
       <c r="R28" t="n">
-        <v>6378203</v>
+        <v>6378202</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3785,7 +3792,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119950738</v>
+        <v>119951024</v>
       </c>
       <c r="B29" t="n">
         <v>79160</v>
@@ -3828,10 +3835,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588797</v>
+        <v>588886</v>
       </c>
       <c r="R29" t="n">
-        <v>6378202</v>
+        <v>6377979</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3901,7 +3908,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950713</v>
+        <v>119950786</v>
       </c>
       <c r="B30" t="n">
         <v>79160</v>
@@ -3944,10 +3951,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588800</v>
+        <v>588866</v>
       </c>
       <c r="R30" t="n">
-        <v>6378217</v>
+        <v>6378218</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4017,10 +4024,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119951000</v>
+        <v>119950809</v>
       </c>
       <c r="B31" t="n">
-        <v>91902</v>
+        <v>79160</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4033,28 +4040,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -4064,10 +4067,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588820</v>
+        <v>588881</v>
       </c>
       <c r="R31" t="n">
-        <v>6378230</v>
+        <v>6378203</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4137,10 +4140,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119950873</v>
+        <v>119951014</v>
       </c>
       <c r="B32" t="n">
-        <v>79160</v>
+        <v>91850</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4153,24 +4156,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -4180,10 +4187,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588864</v>
+        <v>589030</v>
       </c>
       <c r="R32" t="n">
-        <v>6378060</v>
+        <v>6377964</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4253,7 +4260,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119950786</v>
+        <v>119950865</v>
       </c>
       <c r="B33" t="n">
         <v>79160</v>
@@ -4296,10 +4303,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588866</v>
+        <v>588863</v>
       </c>
       <c r="R33" t="n">
-        <v>6378218</v>
+        <v>6378059</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4369,7 +4376,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119951024</v>
+        <v>119950915</v>
       </c>
       <c r="B34" t="n">
         <v>79160</v>
@@ -4412,10 +4419,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588886</v>
+        <v>588998</v>
       </c>
       <c r="R34" t="n">
-        <v>6377979</v>
+        <v>6377948</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4485,10 +4492,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119950884</v>
+        <v>119950796</v>
       </c>
       <c r="B35" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4501,28 +4508,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4532,10 +4535,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588870</v>
+        <v>588888</v>
       </c>
       <c r="R35" t="n">
-        <v>6377977</v>
+        <v>6378207</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4605,10 +4608,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119950865</v>
+        <v>119950815</v>
       </c>
       <c r="B36" t="n">
-        <v>79160</v>
+        <v>94704</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4617,30 +4620,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4648,10 +4652,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588863</v>
+        <v>588881</v>
       </c>
       <c r="R36" t="n">
-        <v>6378059</v>
+        <v>6378203</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4721,7 +4725,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119951055</v>
+        <v>119950713</v>
       </c>
       <c r="B37" t="n">
         <v>79160</v>
@@ -4764,10 +4768,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588879</v>
+        <v>588800</v>
       </c>
       <c r="R37" t="n">
-        <v>6377973</v>
+        <v>6378217</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4837,10 +4841,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119951014</v>
+        <v>119950823</v>
       </c>
       <c r="B38" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4853,28 +4857,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589030</v>
+        <v>588879</v>
       </c>
       <c r="R38" t="n">
-        <v>6377964</v>
+        <v>6378129</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119951055</v>
+        <v>119950815</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>94704</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,30 +2857,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2888,10 +2889,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588879</v>
+        <v>588881</v>
       </c>
       <c r="R21" t="n">
-        <v>6377973</v>
+        <v>6378203</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3078,10 +3079,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119950873</v>
+        <v>119950884</v>
       </c>
       <c r="B23" t="n">
-        <v>79160</v>
+        <v>90600</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3094,24 +3095,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3121,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588864</v>
+        <v>588870</v>
       </c>
       <c r="R23" t="n">
-        <v>6378060</v>
+        <v>6377977</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3316,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119951000</v>
+        <v>119950786</v>
       </c>
       <c r="B25" t="n">
-        <v>91902</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,28 +3337,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3363,10 +3364,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588820</v>
+        <v>588866</v>
       </c>
       <c r="R25" t="n">
-        <v>6378230</v>
+        <v>6378218</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3436,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119950884</v>
+        <v>119950809</v>
       </c>
       <c r="B26" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,28 +3453,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3483,10 +3480,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588870</v>
+        <v>588881</v>
       </c>
       <c r="R26" t="n">
-        <v>6377977</v>
+        <v>6378203</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3556,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119951016</v>
+        <v>119950915</v>
       </c>
       <c r="B27" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3572,28 +3569,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3603,10 +3596,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589034</v>
+        <v>588998</v>
       </c>
       <c r="R27" t="n">
-        <v>6377962</v>
+        <v>6377948</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3676,7 +3669,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119950738</v>
+        <v>119951024</v>
       </c>
       <c r="B28" t="n">
         <v>79160</v>
@@ -3719,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588797</v>
+        <v>588886</v>
       </c>
       <c r="R28" t="n">
-        <v>6378202</v>
+        <v>6377979</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3792,7 +3785,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119951024</v>
+        <v>119950823</v>
       </c>
       <c r="B29" t="n">
         <v>79160</v>
@@ -3835,10 +3828,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588886</v>
+        <v>588879</v>
       </c>
       <c r="R29" t="n">
-        <v>6377979</v>
+        <v>6378129</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3908,7 +3901,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119950786</v>
+        <v>119950713</v>
       </c>
       <c r="B30" t="n">
         <v>79160</v>
@@ -3951,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588866</v>
+        <v>588800</v>
       </c>
       <c r="R30" t="n">
-        <v>6378218</v>
+        <v>6378217</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4024,10 +4017,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119950809</v>
+        <v>119951014</v>
       </c>
       <c r="B31" t="n">
-        <v>79160</v>
+        <v>91850</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4040,24 +4033,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -4067,10 +4064,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588881</v>
+        <v>589030</v>
       </c>
       <c r="R31" t="n">
-        <v>6378203</v>
+        <v>6377964</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4140,7 +4137,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119951014</v>
+        <v>119951016</v>
       </c>
       <c r="B32" t="n">
         <v>91850</v>
@@ -4187,10 +4184,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589030</v>
+        <v>589034</v>
       </c>
       <c r="R32" t="n">
-        <v>6377964</v>
+        <v>6377962</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4376,7 +4373,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119950915</v>
+        <v>119951055</v>
       </c>
       <c r="B34" t="n">
         <v>79160</v>
@@ -4419,10 +4416,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588998</v>
+        <v>588879</v>
       </c>
       <c r="R34" t="n">
-        <v>6377948</v>
+        <v>6377973</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4608,10 +4605,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119950815</v>
+        <v>119951000</v>
       </c>
       <c r="B36" t="n">
-        <v>94704</v>
+        <v>91902</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4620,31 +4617,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588881</v>
+        <v>588820</v>
       </c>
       <c r="R36" t="n">
-        <v>6378203</v>
+        <v>6378230</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119950713</v>
+        <v>119950738</v>
       </c>
       <c r="B37" t="n">
         <v>79160</v>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588800</v>
+        <v>588797</v>
       </c>
       <c r="R37" t="n">
-        <v>6378217</v>
+        <v>6378202</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119950823</v>
+        <v>119950873</v>
       </c>
       <c r="B38" t="n">
         <v>79160</v>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588879</v>
+        <v>588864</v>
       </c>
       <c r="R38" t="n">
-        <v>6378129</v>
+        <v>6378060</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -4725,7 +4725,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119950738</v>
+        <v>119950873</v>
       </c>
       <c r="B37" t="n">
         <v>79160</v>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588797</v>
+        <v>588864</v>
       </c>
       <c r="R37" t="n">
-        <v>6378202</v>
+        <v>6378060</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119950873</v>
+        <v>119950738</v>
       </c>
       <c r="B38" t="n">
         <v>79160</v>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588864</v>
+        <v>588797</v>
       </c>
       <c r="R38" t="n">
-        <v>6378060</v>
+        <v>6378202</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4955,6 +4955,108 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123165337</v>
+      </c>
+      <c r="B39" t="n">
+        <v>56437</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>E22 Målbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>588756</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6378114</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119790043</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119790043</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>123165337</v>
       </c>
       <c r="B39" t="n">
-        <v>56437</v>
+        <v>56440</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119790043</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>123165337</v>
       </c>
       <c r="B39" t="n">
-        <v>56440</v>
+        <v>56446</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119790043</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>123165337</v>
       </c>
       <c r="B39" t="n">
-        <v>56446</v>
+        <v>56449</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 33351-2024 artfynd.xlsx
+++ b/artfynd/A 33351-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119790043</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
